--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB NOVASCHOOL RINCÓN DE LA VICTORIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB NOVASCHOOL RINCÓN DE LA VICTORIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>64.4969</v>
+        <v>40.3767</v>
       </c>
       <c r="E2" t="n">
-        <v>68.8447</v>
+        <v>51.1264</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.3481</v>
+        <v>-10.75</v>
       </c>
       <c r="G2" t="n">
-        <v>21.4362</v>
+        <v>31.1946</v>
       </c>
       <c r="H2" t="n">
-        <v>21.0777</v>
+        <v>16.4762</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3584000000000003</v>
+        <v>14.7182</v>
       </c>
       <c r="J2" t="n">
-        <v>45.7742</v>
+        <v>63.9302</v>
       </c>
       <c r="K2" t="n">
-        <v>34.7861</v>
+        <v>39.3232</v>
       </c>
       <c r="L2" t="n">
-        <v>10.9878</v>
+        <v>24.607</v>
       </c>
       <c r="M2" t="n">
-        <v>-24.3377</v>
+        <v>-32.7356</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.7084</v>
+        <v>-22.8471</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.6292</v>
+        <v>-9.888199999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>24.1833</v>
+        <v>-39.0499</v>
       </c>
       <c r="Q2" t="n">
-        <v>-18.038</v>
+        <v>-81.66759999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>42.2219</v>
+        <v>42.6181</v>
       </c>
       <c r="S2" t="n">
-        <v>38.0499</v>
+        <v>1.4266</v>
       </c>
       <c r="T2" t="n">
-        <v>38.7804</v>
+        <v>1.6636</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7303999999999999</v>
+        <v>-0.2371</v>
       </c>
       <c r="V2" t="n">
-        <v>-19.1731</v>
+        <v>46.8057</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3287</v>
+        <v>67.2008</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.5018</v>
+        <v>-20.3953</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>45.7171</v>
+        <v>39.193</v>
       </c>
       <c r="E3" t="n">
-        <v>38.378</v>
+        <v>43.9747</v>
       </c>
       <c r="F3" t="n">
-        <v>7.338900000000001</v>
+        <v>-4.7815</v>
       </c>
       <c r="G3" t="n">
-        <v>17.5235</v>
+        <v>21.4362</v>
       </c>
       <c r="H3" t="n">
-        <v>13.21</v>
+        <v>21.0777</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3135</v>
+        <v>0.3584000000000003</v>
       </c>
       <c r="J3" t="n">
-        <v>37.6437</v>
+        <v>45.7742</v>
       </c>
       <c r="K3" t="n">
-        <v>27.7583</v>
+        <v>34.7861</v>
       </c>
       <c r="L3" t="n">
-        <v>9.885199999999999</v>
+        <v>10.9878</v>
       </c>
       <c r="M3" t="n">
-        <v>-20.1199</v>
+        <v>-24.3377</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.5483</v>
+        <v>-13.7084</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.5715</v>
+        <v>-10.6292</v>
       </c>
       <c r="P3" t="n">
-        <v>14.4703</v>
+        <v>24.1833</v>
       </c>
       <c r="Q3" t="n">
-        <v>-21.0114</v>
+        <v>-18.038</v>
       </c>
       <c r="R3" t="n">
-        <v>35.482</v>
+        <v>42.2219</v>
       </c>
       <c r="S3" t="n">
-        <v>14.5532</v>
+        <v>12.7464</v>
       </c>
       <c r="T3" t="n">
-        <v>11.3754</v>
+        <v>13.9101</v>
       </c>
       <c r="U3" t="n">
-        <v>3.1779</v>
+        <v>-1.1635</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-19.1731</v>
       </c>
       <c r="W3" t="n">
-        <v>10.3711</v>
+        <v>2.3287</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.2011</v>
+        <v>-21.5018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>25.673</v>
+        <v>38.1687</v>
       </c>
       <c r="E4" t="n">
-        <v>41.5483</v>
+        <v>32.5285</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.8752</v>
+        <v>5.640499999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>31.1946</v>
+        <v>17.5235</v>
       </c>
       <c r="H4" t="n">
-        <v>16.4762</v>
+        <v>13.21</v>
       </c>
       <c r="I4" t="n">
-        <v>14.7182</v>
+        <v>4.3135</v>
       </c>
       <c r="J4" t="n">
-        <v>63.9302</v>
+        <v>37.6437</v>
       </c>
       <c r="K4" t="n">
-        <v>39.3232</v>
+        <v>27.7583</v>
       </c>
       <c r="L4" t="n">
-        <v>24.607</v>
+        <v>9.885199999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-32.7356</v>
+        <v>-20.1199</v>
       </c>
       <c r="N4" t="n">
-        <v>-22.8471</v>
+        <v>-14.5483</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.888199999999999</v>
+        <v>-5.5715</v>
       </c>
       <c r="P4" t="n">
-        <v>-39.0499</v>
+        <v>14.4703</v>
       </c>
       <c r="Q4" t="n">
-        <v>-81.66759999999999</v>
+        <v>-21.0114</v>
       </c>
       <c r="R4" t="n">
-        <v>42.6181</v>
+        <v>35.482</v>
       </c>
       <c r="S4" t="n">
-        <v>-13.2771</v>
+        <v>7.0051</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.9146</v>
+        <v>5.5254</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.3626</v>
+        <v>1.4796</v>
       </c>
       <c r="V4" t="n">
-        <v>46.8057</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>67.2008</v>
+        <v>10.3711</v>
       </c>
       <c r="X4" t="n">
-        <v>-20.3953</v>
+        <v>-11.2011</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>H. DOMINGUEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.642099999999997</v>
+        <v>0.0308</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.8968</v>
+        <v>-0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>18.5384</v>
+        <v>0.3408</v>
       </c>
       <c r="G6" t="n">
-        <v>-21.6858</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-14.546</v>
+        <v>0.4021</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.1398</v>
+        <v>0.4171</v>
       </c>
       <c r="J6" t="n">
-        <v>13.3948</v>
+        <v>0.7436</v>
       </c>
       <c r="K6" t="n">
-        <v>11.269</v>
+        <v>0.0605</v>
       </c>
       <c r="L6" t="n">
-        <v>2.125500000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-35.0805</v>
+        <v>0.0756</v>
       </c>
       <c r="N6" t="n">
-        <v>-25.8151</v>
+        <v>0.3415</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.2653</v>
+        <v>-0.266</v>
       </c>
       <c r="P6" t="n">
-        <v>9.118399999999999</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-32.5081</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>41.6269</v>
+        <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>22.9784</v>
+        <v>-0.1937</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9339</v>
+        <v>-0.0624</v>
       </c>
       <c r="U6" t="n">
-        <v>20.0447</v>
+        <v>-0.1313</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.7689</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.283600000000001</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.0526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. DOMINGUEZ GONZALEZ</t>
+          <t>R. GARCIA CABANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0534</v>
+        <v>-1.6505</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.31</v>
+        <v>-0.7359</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2565</v>
+        <v>-0.9146</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8191000000000001</v>
+        <v>-2.0622</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4021</v>
+        <v>0.4843</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4171</v>
+        <v>-2.5465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7436</v>
+        <v>-0.3424</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0605</v>
+        <v>0.3367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6830000000000001</v>
+        <v>-0.6791</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0756</v>
+        <v>-1.7198</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3415</v>
+        <v>0.1476</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.266</v>
+        <v>-1.8674</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2779</v>
+        <v>0.4801</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0624</v>
+        <v>0.5976</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2155</v>
+        <v>-0.1176</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GARCIA CABANA</t>
+          <t>E. IBADIN SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6423</v>
+        <v>-4.9793</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3846000000000001</v>
+        <v>-3.2058</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0269</v>
+        <v>-1.7735</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0622</v>
+        <v>-4.313</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4843</v>
+        <v>-2.6427</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5465</v>
+        <v>-1.6704</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3424</v>
+        <v>-1.3339</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3367</v>
+        <v>-1.3779</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6791</v>
+        <v>0.04400000000000004</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7198</v>
+        <v>-2.9793</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1476</v>
+        <v>-1.2648</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8674</v>
+        <v>-1.7144</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>-0.1983</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4883</v>
+        <v>-0.4679</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7182</v>
+        <v>0.1103</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2299</v>
+        <v>-0.5782999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERRERA</t>
+          <t>M. ZEA GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3912</v>
+        <v>-5.8977</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8630000000000002</v>
+        <v>-2.304</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5285</v>
+        <v>-3.5937</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.3249</v>
+        <v>-2.2438</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.5306</v>
+        <v>-1.4459</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7942</v>
+        <v>-0.7977999999999998</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.809</v>
+        <v>-0.3090000000000002</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0501</v>
+        <v>-0.3090000000000002</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2411</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.5158</v>
+        <v>-1.9347</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.4806</v>
+        <v>-1.1368</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0354</v>
+        <v>-0.7977999999999998</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3876</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5769</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1495</v>
+        <v>-0.0504</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8689</v>
+        <v>-0.0127</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.0377</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6034999999999999</v>
+        <v>-2.4142</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8701</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. IBADIN SANCHEZ</t>
+          <t>J. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8996</v>
+        <v>-6.0022</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7983</v>
+        <v>-2.4929</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1014</v>
+        <v>-3.5096</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.313</v>
+        <v>-6.3249</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6427</v>
+        <v>-5.5306</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6704</v>
+        <v>-0.7942</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3339</v>
+        <v>-1.809</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3779</v>
+        <v>-2.0501</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04400000000000004</v>
+        <v>0.2411</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9793</v>
+        <v>-4.5158</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2648</v>
+        <v>-3.4806</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7144</v>
+        <v>-1.0354</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1983</v>
+        <v>1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>2.5769</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3883</v>
+        <v>-0.4615</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5177999999999999</v>
+        <v>0.2388999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9061</v>
+        <v>-0.7004</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6034999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.253499999999999</v>
+        <v>-9.466199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7385</v>
+        <v>-15.3888</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.9922</v>
+        <v>5.9228</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8263</v>
+        <v>-21.6858</v>
       </c>
       <c r="H11" t="n">
-        <v>-12.6943</v>
+        <v>-14.546</v>
       </c>
       <c r="I11" t="n">
-        <v>9.8681</v>
+        <v>-7.1398</v>
       </c>
       <c r="J11" t="n">
-        <v>20.5835</v>
+        <v>13.3948</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5464</v>
+        <v>11.269</v>
       </c>
       <c r="L11" t="n">
-        <v>15.0369</v>
+        <v>2.125500000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-23.4096</v>
+        <v>-35.0805</v>
       </c>
       <c r="N11" t="n">
-        <v>-18.2409</v>
+        <v>-25.8151</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.168900000000001</v>
+        <v>-9.2653</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1713</v>
+        <v>9.118399999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-44.2035</v>
+        <v>-32.5081</v>
       </c>
       <c r="R11" t="n">
-        <v>47.3751</v>
+        <v>41.6269</v>
       </c>
       <c r="S11" t="n">
-        <v>11.1055</v>
+        <v>8.8703</v>
       </c>
       <c r="T11" t="n">
-        <v>18.4725</v>
+        <v>1.441</v>
       </c>
       <c r="U11" t="n">
-        <v>-7.367</v>
+        <v>7.428599999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-17.7044</v>
+        <v>-5.7689</v>
       </c>
       <c r="W11" t="n">
-        <v>7.8866</v>
+        <v>2.283600000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-25.5908</v>
+        <v>-8.0526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ZEA GONZALEZ</t>
+          <t>I. MARTIN ARROYO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.649299999999999</v>
+        <v>-9.9841</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9152</v>
+        <v>-10.1138</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7341</v>
+        <v>0.1298999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2438</v>
+        <v>-10.9819</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4459</v>
+        <v>-6.601100000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7977999999999998</v>
+        <v>-4.3809</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3090000000000002</v>
+        <v>-7.8614</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3090000000000002</v>
+        <v>-4.397</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-3.4643</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9347</v>
+        <v>-3.1204</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1368</v>
+        <v>-2.2039</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7977999999999998</v>
+        <v>-0.9165</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1893</v>
+        <v>0.5946</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-2.1804</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7929</v>
+        <v>2.775</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8021</v>
+        <v>1.751</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.624</v>
+        <v>1.2759</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1781</v>
+        <v>0.4753000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4142</v>
+        <v>-1.348</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1.348</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. MARTIN ARROYO</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.2071</v>
+        <v>-12.8541</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.2574</v>
+        <v>-8.1357</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05020000000000024</v>
+        <v>-4.7181</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.9819</v>
+        <v>-2.8263</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.601100000000001</v>
+        <v>-12.6943</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.3809</v>
+        <v>9.8681</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.8614</v>
+        <v>20.5835</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.397</v>
+        <v>5.5464</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.4643</v>
+        <v>15.0369</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1204</v>
+        <v>-23.4096</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2039</v>
+        <v>-18.2409</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9165</v>
+        <v>-5.168900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5946</v>
+        <v>3.1713</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1804</v>
+        <v>-44.2035</v>
       </c>
       <c r="R13" t="n">
-        <v>2.775</v>
+        <v>47.3751</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5279999999999999</v>
+        <v>4.5052</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1323</v>
+        <v>7.5984</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3954</v>
+        <v>-3.0933</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.348</v>
+        <v>-17.7044</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.348</v>
+        <v>7.8866</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-25.5908</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.4187</v>
+        <v>-20.2117</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.8681</v>
+        <v>-11.0073</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.5503</v>
+        <v>-9.2049</v>
       </c>
       <c r="G14" t="n">
         <v>-5.158099999999999</v>
@@ -1546,13 +1546,13 @@
         <v>25.769</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.1938</v>
+        <v>-3.9872</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.3833</v>
+        <v>-1.5224</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.810700000000001</v>
+        <v>-2.4651</v>
       </c>
       <c r="V14" t="n">
         <v>-10.472</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.8703</v>
+        <v>-21.0979</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.0589</v>
+        <v>-13.9054</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.8114</v>
+        <v>-7.1929</v>
       </c>
       <c r="G15" t="n">
-        <v>-33.1366</v>
+        <v>-18.7952</v>
       </c>
       <c r="H15" t="n">
-        <v>-27.333</v>
+        <v>5.035800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.8034</v>
+        <v>-23.831</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4437000000000004</v>
+        <v>12.3237</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.0465</v>
+        <v>28.0149</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4907</v>
+        <v>-15.6914</v>
       </c>
       <c r="M15" t="n">
-        <v>-33.5801</v>
+        <v>-31.1193</v>
       </c>
       <c r="N15" t="n">
-        <v>-24.2862</v>
+        <v>-22.9791</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.294</v>
+        <v>-8.139899999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>16.849</v>
+        <v>-7.532299999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-24.1829</v>
+        <v>-48.1676</v>
       </c>
       <c r="R15" t="n">
-        <v>41.032</v>
+        <v>40.6357</v>
       </c>
       <c r="S15" t="n">
-        <v>-14.7199</v>
+        <v>-0.2425999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.62</v>
+        <v>-0.9105</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.1</v>
+        <v>0.6675</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.863</v>
+        <v>5.472</v>
       </c>
       <c r="W15" t="n">
-        <v>10.3009</v>
+        <v>22.8496</v>
       </c>
       <c r="X15" t="n">
-        <v>-14.1635</v>
+        <v>-17.3775</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-34.8794</v>
+        <v>-23.1369</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.8055</v>
+        <v>-11.9879</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.0737</v>
+        <v>-11.1492</v>
       </c>
       <c r="G16" t="n">
-        <v>-18.7952</v>
+        <v>-33.1366</v>
       </c>
       <c r="H16" t="n">
-        <v>5.035800000000001</v>
+        <v>-27.333</v>
       </c>
       <c r="I16" t="n">
-        <v>-23.831</v>
+        <v>-5.8034</v>
       </c>
       <c r="J16" t="n">
-        <v>12.3237</v>
+        <v>0.4437000000000004</v>
       </c>
       <c r="K16" t="n">
-        <v>28.0149</v>
+        <v>-3.0465</v>
       </c>
       <c r="L16" t="n">
-        <v>-15.6914</v>
+        <v>3.4907</v>
       </c>
       <c r="M16" t="n">
-        <v>-31.1193</v>
+        <v>-33.5801</v>
       </c>
       <c r="N16" t="n">
-        <v>-22.9791</v>
+        <v>-24.2862</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.139899999999999</v>
+        <v>-9.294</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.532299999999999</v>
+        <v>16.849</v>
       </c>
       <c r="Q16" t="n">
-        <v>-48.1676</v>
+        <v>-24.1829</v>
       </c>
       <c r="R16" t="n">
-        <v>40.6357</v>
+        <v>41.032</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.0239</v>
+        <v>-2.9867</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.8111</v>
+        <v>1.451</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.2129</v>
+        <v>-4.4378</v>
       </c>
       <c r="V16" t="n">
-        <v>5.472</v>
+        <v>-3.863</v>
       </c>
       <c r="W16" t="n">
-        <v>22.8496</v>
+        <v>10.3009</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.3775</v>
+        <v>-14.1635</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-36.4172</v>
+        <v>-27.9639</v>
       </c>
       <c r="E17" t="n">
-        <v>-31.1684</v>
+        <v>-29.5462</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.248699999999999</v>
+        <v>1.582400000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-37.5047</v>
+        <v>-25.7749</v>
       </c>
       <c r="H17" t="n">
-        <v>-19.9431</v>
+        <v>-17.0219</v>
       </c>
       <c r="I17" t="n">
-        <v>-17.5613</v>
+        <v>-8.7529</v>
       </c>
       <c r="J17" t="n">
-        <v>-18.1996</v>
+        <v>-11.856</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.0735</v>
+        <v>-6.0252</v>
       </c>
       <c r="L17" t="n">
-        <v>-12.1257</v>
+        <v>-5.8306</v>
       </c>
       <c r="M17" t="n">
-        <v>-19.3052</v>
+        <v>-13.9188</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.8695</v>
+        <v>-10.9967</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.4356</v>
+        <v>-2.9226</v>
       </c>
       <c r="P17" t="n">
-        <v>16.0561</v>
+        <v>18.4348</v>
       </c>
       <c r="Q17" t="n">
-        <v>-14.2719</v>
+        <v>-23.39</v>
       </c>
       <c r="R17" t="n">
-        <v>30.3281</v>
+        <v>41.825</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.4601</v>
+        <v>-2.6328</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9552000000000006</v>
+        <v>-0.3204999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5044</v>
+        <v>-2.3119</v>
       </c>
       <c r="V17" t="n">
-        <v>-12.509</v>
+        <v>-17.9907</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2582</v>
+        <v>6.0205</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.7672</v>
+        <v>-24.0113</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-41.9906</v>
+        <v>-32.6433</v>
       </c>
       <c r="E18" t="n">
-        <v>-40.4885</v>
+        <v>-28.9771</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5021</v>
+        <v>-3.6666</v>
       </c>
       <c r="G18" t="n">
-        <v>-25.7749</v>
+        <v>-37.5047</v>
       </c>
       <c r="H18" t="n">
-        <v>-17.0219</v>
+        <v>-19.9431</v>
       </c>
       <c r="I18" t="n">
-        <v>-8.7529</v>
+        <v>-17.5613</v>
       </c>
       <c r="J18" t="n">
-        <v>-11.856</v>
+        <v>-18.1996</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.0252</v>
+        <v>-6.0735</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.8306</v>
+        <v>-12.1257</v>
       </c>
       <c r="M18" t="n">
-        <v>-13.9188</v>
+        <v>-19.3052</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.9967</v>
+        <v>-13.8695</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.9226</v>
+        <v>-5.4356</v>
       </c>
       <c r="P18" t="n">
-        <v>18.4348</v>
+        <v>16.0561</v>
       </c>
       <c r="Q18" t="n">
-        <v>-23.39</v>
+        <v>-14.2719</v>
       </c>
       <c r="R18" t="n">
-        <v>41.825</v>
+        <v>30.3281</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.6596</v>
+        <v>1.3138</v>
       </c>
       <c r="T18" t="n">
-        <v>-11.2626</v>
+        <v>1.2363</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.3968</v>
+        <v>0.07729999999999992</v>
       </c>
       <c r="V18" t="n">
-        <v>-17.9907</v>
+        <v>-12.509</v>
       </c>
       <c r="W18" t="n">
-        <v>6.0205</v>
+        <v>2.2582</v>
       </c>
       <c r="X18" t="n">
-        <v>-24.0113</v>
+        <v>-14.7672</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-64.1683</v>
+        <v>-49.2218</v>
       </c>
       <c r="E19" t="n">
-        <v>-65.6173</v>
+        <v>-53.9621</v>
       </c>
       <c r="F19" t="n">
-        <v>1.449199999999999</v>
+        <v>4.7402</v>
       </c>
       <c r="G19" t="n">
         <v>-26.2161</v>
@@ -1936,13 +1936,13 @@
         <v>44.6004</v>
       </c>
       <c r="S19" t="n">
-        <v>-22.8084</v>
+        <v>-7.862500000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.4682</v>
+        <v>-1.8129</v>
       </c>
       <c r="U19" t="n">
-        <v>-9.3405</v>
+        <v>-6.0495</v>
       </c>
       <c r="V19" t="n">
         <v>7.453899999999999</v>
@@ -1969,19 +1969,19 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-123.2556</v>
+        <v>-98.2842</v>
       </c>
       <c r="E20" t="n">
-        <v>-66.09709999999998</v>
+        <v>-55.38709999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-57.1594</v>
+        <v>-42.898</v>
       </c>
       <c r="G20" t="n">
         <v>-116.9939</v>
       </c>
       <c r="H20" t="n">
-        <v>-67.81100000000001</v>
+        <v>-67.81099999999999</v>
       </c>
       <c r="I20" t="n">
         <v>-49.1825</v>
@@ -1993,7 +1993,7 @@
         <v>135.1058</v>
       </c>
       <c r="L20" t="n">
-        <v>30.43010000000001</v>
+        <v>30.4301</v>
       </c>
       <c r="M20" t="n">
         <v>-282.5289</v>
@@ -2002,7 +2002,7 @@
         <v>-202.9169</v>
       </c>
       <c r="O20" t="n">
-        <v>-79.6123</v>
+        <v>-79.61229999999999</v>
       </c>
       <c r="P20" t="n">
         <v>32.70699999999999</v>
@@ -2014,16 +2014,16 @@
         <v>443.0287</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.758300000000002</v>
+        <v>19.2132</v>
       </c>
       <c r="T20" t="n">
-        <v>19.698</v>
+        <v>30.4071</v>
       </c>
       <c r="U20" t="n">
-        <v>-25.4562</v>
+        <v>-11.1952</v>
       </c>
       <c r="V20" t="n">
-        <v>-33.21190000000001</v>
+        <v>-33.2119</v>
       </c>
       <c r="W20" t="n">
         <v>158.9918</v>
